--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW2"/>
+  <dimension ref="A1:AW3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -510,7 +510,7 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
@@ -851,10 +851,8 @@
           <t>PRAMOD YADAV</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9851202417</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9851202417</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -944,10 +942,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -958,32 +954,243 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS2" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT2" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 16m</t>
+        </is>
+      </c>
+      <c r="AU2" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV2" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS2" s="3" t="inlineStr">
+      <c r="AW2" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376631</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Raut</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Raut</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9861569905</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57:25 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9861569905</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:21:09 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57:25 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.657741</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Unnamed Road, M958+5CJ, Mahalaxmi 44600, Near by Shree Jana Sneha Krishi Bahu Udesya Sahakari Sansth</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>rautnirajan306@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>09:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sagar Khadka</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L27-6</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.366226</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT2" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 16m</t>
-        </is>
-      </c>
-      <c r="AU2" s="3" t="inlineStr">
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>23h 36m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV2" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="AW2" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -998,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1035,7 +1242,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -1045,7 +1252,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -1080,7 +1287,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 1h 16m</t>
+          <t>1d 26m</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1324,7 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1132,203 +1339,311 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E13" s="4" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="C16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I19" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L17" s="4" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M17" s="4" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>TKT1376513</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>PRAMOD YADAV</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>IPTV Remote damage Issue</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
         <is>
           <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>23 Oct 2026 10:02:39 AM</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
-      <c r="L18" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M18" s="3" t="inlineStr">
+      <c r="M20" s="3" t="inlineStr">
         <is>
           <t>1d 1h 16m</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>TKT1376631</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Nirajan Raut</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57:25 AM</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:21:09 PM</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57:25 AM</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>23h 36m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1050,10 +1050,8 @@
           <t>Nirajan Raut</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9861569905</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9861569905</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1088,10 +1086,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.657741</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.657741</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1147,25 +1143,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L27-6</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.366226</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.366226</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">
@@ -1214,7 +1206,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1613,7 +1605,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW3"/>
+  <dimension ref="A1:AW4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -494,7 +494,7 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="15" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -523,18 +523,18 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="15" customWidth="1" min="38" max="38"/>
+    <col width="22" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1183,6 +1183,209 @@
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36 PM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Wifi - 6 Router Instal</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376706</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Ashok tamang</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Ashok tamang</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9865115046</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>BKT9865115046</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:17:45 PM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Lokenthali 3 kune, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9865115046@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>08:19 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Rajnikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>22h 18m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1206,7 +1409,7 @@
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1234,7 +1437,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1244,7 +1447,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -1279,7 +1482,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 26m</t>
+          <t>23h 43m</t>
         </is>
       </c>
     </row>
@@ -1320,10 +1523,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
@@ -1396,10 +1599,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -1636,6 +1839,73 @@
       <c r="M21" s="5" t="inlineStr">
         <is>
           <t>23h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376706</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Ashok tamang</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:17:45 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>22h 18m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW4"/>
+  <dimension ref="A1:AW5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -513,12 +513,12 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="15" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="29" customWidth="1" min="32" max="32"/>
-    <col width="27" customWidth="1" min="33" max="33"/>
+    <col width="30" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -1253,10 +1253,8 @@
           <t>Ashok tamang</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9865115046</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9865115046</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1346,10 +1344,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
@@ -1360,30 +1356,241 @@
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>22h 18m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>22h 18m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:44 PM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376730</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>9841519997</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:14:20 PM</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>9841519997</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:09:37 PM</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:44:37 PM</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>27.720628</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC5" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr">
+        <is>
+          <t>RB Inn - Hotel Nagarjun 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="inlineStr">
+        <is>
+          <t>awesomeland0132@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG5" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr">
+        <is>
+          <t>07:35 hour</t>
+        </is>
+      </c>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr">
+        <is>
+          <t>Pramila Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>CDB428</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>85.279862</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>21h 30m</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>21h 35m</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
@@ -1400,13 +1607,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -1437,7 +1644,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -1447,7 +1654,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -1470,7 +1677,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>5h 22m</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1689,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 43m</t>
+          <t>23h 11m</t>
         </is>
       </c>
     </row>
@@ -1541,10 +1748,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -1633,167 +1840,123 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K19" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L19" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M19" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>TKT1376513</t>
-        </is>
-      </c>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>PRAMOD YADAV</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 10:02:39 AM</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>TKT1376631</t>
+          <t>TKT1376513</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Nirajan Raut</t>
+          <t>PRAMOD YADAV</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1813,22 +1976,22 @@
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 12:21:09 PM</t>
+          <t>23 Oct 2026 10:02:39 AM</t>
         </is>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="L21" s="5" t="inlineStr">
@@ -1838,74 +2001,208 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>23h 36m</t>
+          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>TKT1376631</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Raut</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57:25 AM</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 12:21:09 PM</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:57:25 AM</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>23h 36m</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
           <t>TKT1376706</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Ashok tamang</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>24 Oct 2026 12:36:01 PM</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 02:17:45 PM</t>
         </is>
       </c>
-      <c r="K22" s="3" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>24 Oct 2026 12:36:01 PM</t>
         </is>
       </c>
-      <c r="L22" s="3" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M22" s="3" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>22h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376730</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:14:20 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:09:37 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:44:37 PM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>21h 30m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>21h 35m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1452,10 +1452,8 @@
           <t>Binir Kayastha Shrestha</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>9841519997</t>
-        </is>
+      <c r="O5" s="3" t="n">
+        <v>9841519997</v>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
@@ -1490,10 +1488,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="inlineStr">
-        <is>
-          <t>27.720628</t>
-        </is>
+      <c r="Y5" s="3" t="n">
+        <v>27.720628</v>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
@@ -1549,25 +1545,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN5" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
           <t>CDB428</t>
         </is>
       </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>85.279862</t>
-        </is>
+      <c r="AP5" s="3" t="n">
+        <v>85.27986199999999</v>
       </c>
       <c r="AQ5" s="3" t="inlineStr"/>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
@@ -1616,7 +1608,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2172,7 +2164,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW5"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="24" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="11" customWidth="1" min="29" max="29"/>
     <col width="10" customWidth="1" min="30" max="30"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1585,6 +1585,217 @@
       <c r="AW5" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV not working</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373677</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Shrestha</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Shrestha</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9851013189</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:22:54 PM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9851013189</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:25:13 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:22:54 PM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.65171</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-customer care</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr">
+        <is>
+          <t>Problem</t>
+        </is>
+      </c>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>New Millennium School,J8XX+M2V, Mahalaxmi , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>shrestha143nisha@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>10:57 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr"/>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>2,7</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.34641</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>6d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1608,7 +1819,7 @@
     <col width="31" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -1636,7 +1847,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -1646,7 +1857,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -1669,7 +1880,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 22m</t>
+          <t>4h 18m</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1892,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>23h 11m</t>
+          <t>2d 3h 56m</t>
         </is>
       </c>
     </row>
@@ -1740,10 +1951,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -1840,7 +2051,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -1855,167 +2066,123 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L20" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M20" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>TKT1376513</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>PRAMOD YADAV</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 10:02:39 AM</t>
-        </is>
-      </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="L21" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M21" s="5" t="inlineStr">
-        <is>
-          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>TKT1376631</t>
+          <t>TKT1376513</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Nirajan Raut</t>
+          <t>PRAMOD YADAV</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2035,22 +2202,22 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t>23 Oct 2026 12:21:09 PM</t>
+          <t>23 Oct 2026 10:02:39 AM</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
@@ -2060,19 +2227,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>23h 36m</t>
+          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TKT1376706</t>
+          <t>TKT1376631</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Ashok tamang</t>
+          <t>Nirajan Raut</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2102,22 +2269,22 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 02:17:45 PM</t>
+          <t>23 Oct 2026 12:21:09 PM</t>
         </is>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="L23" s="5" t="inlineStr">
@@ -2127,74 +2294,208 @@
       </c>
       <c r="M23" s="5" t="inlineStr">
         <is>
-          <t>22h 18m</t>
+          <t>23h 36m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>TKT1376706</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Ashok tamang</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:17:45 PM</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>22h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>TKT1376730</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Binir Kayastha Shrestha</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Router Adaptor damage Issue</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr">
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 03:14:20 PM</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 03:09:37 PM</t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>24 Oct 2026 12:44:37 PM</t>
         </is>
       </c>
-      <c r="L24" s="3" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>21h 30m</t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>21h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373677</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Shrestha</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:22:54 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:25:13 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:22:54 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>6d 22h 57m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AW7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <col width="10" customWidth="1" min="30" max="30"/>
     <col width="40" customWidth="1" min="31" max="31"/>
     <col width="29" customWidth="1" min="32" max="32"/>
-    <col width="30" customWidth="1" min="33" max="33"/>
+    <col width="31" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -1655,10 +1655,8 @@
           <t>Nisha Shrestha</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9851013189</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9851013189</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1693,10 +1691,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.65171</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.65171</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1752,50 +1748,249 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>2,7</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.34641</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.34641000000001</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>6d 22h 57m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
           <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>6d 22h 57m</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV6" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 1:34 PM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wifi  range</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376810</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9702616130</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:36:42 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>KLK9702616130</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:29:23 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:34:40 PM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr"/>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Chamati Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>9702616130@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>06:05 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>CDB313</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr"/>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>19h 57m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>20h 5m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -1810,13 +2005,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
     <col width="45" customWidth="1" min="7" max="7"/>
@@ -1847,7 +2042,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -1857,7 +2052,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -1880,7 +2075,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>4h 18m</t>
+          <t>6h 54m</t>
         </is>
       </c>
     </row>
@@ -1892,7 +2087,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2d 3h 56m</t>
+          <t>1d 22h 38m</t>
         </is>
       </c>
     </row>
@@ -1962,80 +2157,75 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
@@ -2051,7 +2241,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
@@ -2074,7 +2264,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -2089,234 +2279,146 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="I23" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L21" s="4" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M21" s="4" t="inlineStr">
+      <c r="M23" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>TKT1376513</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>PRAMOD YADAV</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 10:02:39 AM</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>TKT1376631</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>Nirajan Raut</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
-        </is>
-      </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 12:21:09 PM</t>
-        </is>
-      </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
-        </is>
-      </c>
-      <c r="L23" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M23" s="5" t="inlineStr">
-        <is>
-          <t>23h 36m</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>TKT1376706</t>
+          <t>TKT1376513</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Ashok tamang</t>
+          <t>PRAMOD YADAV</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2336,22 +2438,22 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>23 Oct 2026 02:17:45 PM</t>
+          <t>23 Oct 2026 10:02:39 AM</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -2361,39 +2463,39 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>22h 18m</t>
+          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>TKT1376730</t>
+          <t>TKT1376631</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Binir Kayastha Shrestha</t>
+          <t>Nirajan Raut</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -2403,99 +2505,300 @@
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 03:14:20 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 03:09:37 PM</t>
+          <t>23 Oct 2026 12:21:09 PM</t>
         </is>
       </c>
       <c r="K25" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:44:37 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="L25" s="5" t="inlineStr">
         <is>
-          <t>21h 30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M25" s="5" t="inlineStr">
         <is>
-          <t>21h 35m</t>
+          <t>23h 36m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
+          <t>TKT1376706</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Ashok tamang</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 02:17:45 PM</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:36:01 PM</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>22h 18m</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>TKT1376730</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:14:20 PM</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:09:37 PM</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:44:37 PM</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>21h 30m</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>21h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
           <t>TKT1373677</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>Nisha Shrestha</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>24 Oct 2026 01:22:54 PM</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="J28" s="3" t="inlineStr">
         <is>
           <t>17 Oct 2026 02:25:13 PM</t>
         </is>
       </c>
-      <c r="K26" s="3" t="inlineStr">
+      <c r="K28" s="3" t="inlineStr">
         <is>
           <t>24 Oct 2026 01:22:54 PM</t>
         </is>
       </c>
-      <c r="L26" s="3" t="inlineStr">
+      <c r="L28" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="M26" s="3" t="inlineStr">
+      <c r="M28" s="3" t="inlineStr">
         <is>
           <t>6d 22h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>TKT1376810</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:36:42 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:29:23 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:34:40 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>19h 57m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>20h 5m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1858,10 +1858,8 @@
           <t>Sonim Manandhar</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9702616130</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9702616130</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -1951,10 +1949,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
@@ -1965,7 +1961,7 @@
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2014,7 +2010,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2768,7 +2764,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW7"/>
+  <dimension ref="A1:AW9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -1987,6 +1987,420 @@
       <c r="AW7" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 2:06 PM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377162</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9841221094</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:47:54 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841221094</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:34:32 AM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:06:12 PM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>27.71028449462496, 85.29539256891584, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>9841768213@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>02:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>CDB451</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 2:05 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377162</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9841221094</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:47:54 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841221094</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:34:32 AM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:06:12 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>27.71028449462496, 85.29539256891584, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9841768213@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>02:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>CDB451</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
         </is>
       </c>
     </row>
@@ -2001,7 +2415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2010,7 +2424,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -2038,7 +2452,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -2048,7 +2462,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2071,7 +2485,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>6h 54m</t>
+          <t>5h 45m</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2497,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 22h 38m</t>
+          <t>1d 11h 36m</t>
         </is>
       </c>
     </row>
@@ -2156,95 +2570,90 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
           <t>Wi-Fi Range</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C13" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2260,7 +2669,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
@@ -2283,7 +2692,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2301,12 +2710,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -2321,234 +2730,146 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J23" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K23" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L23" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M23" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>TKT1376513</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>PRAMOD YADAV</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 10:02:39 AM</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="L24" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>TKT1376631</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Nirajan Raut</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 12:21:09 PM</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>23h 36m</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>TKT1376706</t>
+          <t>TKT1376513</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Ashok tamang</t>
+          <t>PRAMOD YADAV</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2568,22 +2889,22 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>23 Oct 2026 02:17:45 PM</t>
+          <t>23 Oct 2026 10:02:39 AM</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
@@ -2593,39 +2914,39 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>22h 18m</t>
+          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>TKT1376730</t>
+          <t>TKT1376631</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Binir Kayastha Shrestha</t>
+          <t>Nirajan Raut</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
@@ -2635,54 +2956,54 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 03:14:20 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 03:09:37 PM</t>
+          <t>23 Oct 2026 12:21:09 PM</t>
         </is>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:44:37 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
         <is>
-          <t>21h 30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M27" s="5" t="inlineStr">
         <is>
-          <t>21h 35m</t>
+          <t>23h 36m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1373677</t>
+          <t>TKT1376706</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Nisha Shrestha</t>
+          <t>Ashok tamang</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -2702,22 +3023,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 01:22:54 PM</t>
+          <t>24 Oct 2026 12:36:01 PM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 02:25:13 PM</t>
+          <t>23 Oct 2026 02:17:45 PM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 01:22:54 PM</t>
+          <t>24 Oct 2026 12:36:01 PM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -2727,74 +3048,342 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>6d 22h 57m</t>
+          <t>22h 18m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>TKT1376730</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Binir Kayastha Shrestha</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Router Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:14:20 PM</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 03:09:37 PM</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 12:44:37 PM</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>21h 30m</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>21h 35m</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1373677</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Shrestha</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:22:54 PM</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>17 Oct 2026 02:25:13 PM</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:22:54 PM</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>6d 22h 57m</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>TKT1376810</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Sonim Manandhar</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Wi-Fi Range</t>
         </is>
       </c>
-      <c r="D29" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F29" s="5" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 05:36:42 PM</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>23 Oct 2026 05:29:23 PM</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>24 Oct 2026 01:34:40 PM</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>19h 57m</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>20h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377162</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:47:54 AM</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:34:32 AM</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:06:12 PM</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TKT1377162</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:47:54 AM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:34:32 AM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:06:12 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
@@ -2057,10 +2057,8 @@
           <t>Jyoti Sharma</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9841221094</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9841221094</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2132,10 +2130,8 @@
           <t>NETTV-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH8" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
@@ -2154,10 +2150,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2168,7 +2162,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
@@ -2264,10 +2258,8 @@
           <t>Jyoti Sharma</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9841221094</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9841221094</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2339,10 +2331,8 @@
           <t>NETTV-Blank TV Display</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2361,10 +2351,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2375,7 +2363,7 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2424,7 +2412,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3286,7 +3274,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
@@ -3353,7 +3341,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW9"/>
+  <dimension ref="A1:AW10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -497,7 +497,7 @@
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
@@ -521,18 +521,18 @@
     <col width="31" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="22" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="40" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
   </cols>
@@ -2389,6 +2389,229 @@
       <c r="AW9" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>router faulty</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1376956</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Pathak</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Pathak</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841495050</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:59:32 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 11: 15:00 AM</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9841495050</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 07:15:29 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:59:32 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.663273</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Thimi-Biruwa Rd, Anantalingeshwar Near By Harsha Chowk, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>nirajanphk@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>04:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr">
+        <is>
+          <t>19:04 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>L15-3</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.392718</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>7h 44m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router faulty   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -2440,7 +2663,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -2461,7 +2684,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>88.9%</t>
         </is>
       </c>
     </row>
@@ -2576,95 +2799,90 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>No Internet Connection</t>
         </is>
       </c>
       <c r="B13" s="5" t="n">
         <v>1</v>
       </c>
       <c r="C13" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="C14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Total Tickets Breakdown by Category &amp; Sub Category</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>Total Scraped Tickets</t>
         </is>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Solved / Handled Count</t>
         </is>
       </c>
-      <c r="E16" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Solution Rate %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IPTV Remote damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
@@ -2680,7 +2898,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
@@ -2703,7 +2921,7 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="C20" s="3" t="n">
@@ -2721,19 +2939,19 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -2744,254 +2962,166 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>Wi-Fi Range</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="I27" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="J27" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L25" s="4" t="inlineStr">
+      <c r="L27" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M25" s="4" t="inlineStr">
+      <c r="M27" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>TKT1376513</t>
-        </is>
-      </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>PRAMOD YADAV</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H26" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 10:02:39 AM</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 16m</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>TKT1376631</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>Nirajan Raut</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 12:21:09 PM</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
-        </is>
-      </c>
-      <c r="L27" s="5" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M27" s="5" t="inlineStr">
-        <is>
-          <t>23h 36m</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>TKT1376706</t>
+          <t>TKT1376513</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Ashok tamang</t>
+          <t>PRAMOD YADAV</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3011,22 +3141,22 @@
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>23 Oct 2026 02:17:45 PM</t>
+          <t>23 Oct 2026 10:02:39 AM</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
@@ -3036,39 +3166,39 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>22h 18m</t>
+          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1376730</t>
+          <t>TKT1376631</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Binir Kayastha Shrestha</t>
+          <t>Nirajan Raut</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
@@ -3078,54 +3208,54 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 03:14:20 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 03:09:37 PM</t>
+          <t>23 Oct 2026 12:21:09 PM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:44:37 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
         <is>
-          <t>21h 30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>21h 35m</t>
+          <t>23h 36m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1373677</t>
+          <t>TKT1376706</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nisha Shrestha</t>
+          <t>Ashok tamang</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3145,22 +3275,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 01:22:54 PM</t>
+          <t>24 Oct 2026 12:36:01 PM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 02:25:13 PM</t>
+          <t>23 Oct 2026 02:17:45 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 01:22:54 PM</t>
+          <t>24 Oct 2026 12:36:01 PM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3170,29 +3300,29 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>6d 22h 57m</t>
+          <t>22h 18m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1376810</t>
+          <t>TKT1376730</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Sonim Manandhar</t>
+          <t>Binir Kayastha Shrestha</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -3212,64 +3342,64 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 05:36:42 PM</t>
+          <t>23 Oct 2026 03:14:20 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 05:29:23 PM</t>
+          <t>23 Oct 2026 03:09:37 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 01:34:40 PM</t>
+          <t>24 Oct 2026 12:44:37 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>19h 57m</t>
+          <t>21h 30m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>20h 5m</t>
+          <t>21h 35m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1377162</t>
+          <t>TKT1373677</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Jyoti Sharma</t>
+          <t>Nisha Shrestha</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -3279,97 +3409,231 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:47:54 AM</t>
+          <t>24 Oct 2026 01:22:54 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:34:32 AM</t>
+          <t>17 Oct 2026 02:25:13 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 02:06:12 PM</t>
+          <t>24 Oct 2026 01:22:54 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>2h 18m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>2h 31m</t>
+          <t>6d 22h 57m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
+          <t>TKT1376810</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Sonim Manandhar</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Wi-Fi Range</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Low Wi-Fi Range on both band</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:36:42 PM</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>23 Oct 2026 05:29:23 PM</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:34:40 PM</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>19h 57m</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>20h 5m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
           <t>TKT1377162</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Jyoti Sharma</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>IPTV Related Issues</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr">
+      <c r="D34" s="3" t="inlineStr">
         <is>
           <t>NETTV-Blank TV Display</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
         <is>
           <t>Closed</t>
         </is>
       </c>
-      <c r="F33" s="5" t="inlineStr">
+      <c r="F34" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>nan</t>
         </is>
       </c>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="I34" s="3" t="inlineStr">
         <is>
           <t>24 Oct 2026 11:47:54 AM</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="J34" s="3" t="inlineStr">
         <is>
           <t>24 Oct 2026 11:34:32 AM</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="K34" s="3" t="inlineStr">
         <is>
           <t>24 Oct 2026 02:06:12 PM</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
         <is>
           <t>2h 18m</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>TKT1377162</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:47:54 AM</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:34:32 AM</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:06:12 PM</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>2h 31m</t>
         </is>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2459,10 +2459,8 @@
           <t>Nirajan Pathak</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841495050</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841495050</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2501,10 +2499,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.663273</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.663273</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2542,10 +2538,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH10" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
@@ -2568,25 +2562,21 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>L15-3</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.392718</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.392718</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : router faulty   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW10"/>
+  <dimension ref="A1:AW12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="40" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -2602,6 +2602,428 @@
       <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 4:01 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377020</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Ranju Nepali</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Ranju Nepali</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9813475180</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 09:04:28 AM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9880534715</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 09:04:28 AM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:01:57 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Glacier International School (school block) - Middle school M8QV+Q39 Thulo Kharibot Marga Kathmandu</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>ranjunepali432@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L22-5</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>6h 57m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>6h 57m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 3:56 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377270</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9841915176</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 03:59:14 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 05: 03:00 PM</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9841915176</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 01:03:33 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 03:59:14 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.669</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Sisha Cafe With Fast Food,Ekatamarga 34, ???????? , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>pragalrock@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>02:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr">
+        <is>
+          <t>21:07 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L24-7</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.34123</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 55m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
         </is>
       </c>
     </row>
@@ -2653,7 +3075,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -2674,7 +3096,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>72.7%</t>
         </is>
       </c>
     </row>
@@ -2739,14 +3161,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +3215,7 @@
         </is>
       </c>
       <c r="B13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>0</v>
@@ -2869,14 +3291,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -2984,7 +3406,7 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
         <v>0</v>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW12"/>
+  <dimension ref="A1:AW13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2672,10 +2672,8 @@
           <t>Ranju Nepali</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9813475180</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9813475180</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2761,10 +2759,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
@@ -2775,7 +2771,7 @@
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
@@ -2871,10 +2867,8 @@
           <t>Pragal Kc</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9841915176</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9841915176</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -2913,10 +2907,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.669</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.669</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -2954,10 +2946,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH12" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH12" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
@@ -2980,48 +2970,243 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L24-7</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.34123</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.34123</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>2h 55m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>2h 55m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 4:03 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377006</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Aakriti Bhandari</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Aakriti Bhandari</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9847902722</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 08:46:06 AM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9847902722</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 08:46:06 AM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:03:45 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Maitidevi chowk , birendra marga, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>bhandaryaakriti9@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Susmita Thapa</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>CDB164</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>7h 17m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>7h 17m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
@@ -3075,7 +3260,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -3096,7 +3281,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -3161,14 +3346,14 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3291,14 +3476,14 @@
         </is>
       </c>
       <c r="C18" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW13"/>
+  <dimension ref="A1:AW14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -496,10 +496,10 @@
     <col width="40" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -3080,10 +3080,8 @@
           <t>Aakriti Bhandari</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9847902722</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9847902722</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3169,10 +3167,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
@@ -3183,32 +3179,235 @@
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>7h 17m</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>7h 17m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
           <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>7h 17m</t>
-        </is>
-      </c>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>7h 17m</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wi-Fi 6   has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 4:31 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>no light on the router</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377051</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur shrestha</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur shrestha</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9841598179</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:31:45 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9841598179</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 09:47:23 AM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:31:45 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>near by Mahalaxmi Party Venue - Banquet hall, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr">
+        <is>
+          <t>birenshrestha.bs@gmail.co</t>
+        </is>
+      </c>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>06:31 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>CDB931</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>6h 44m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M35"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -3232,7 +3431,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -3260,7 +3459,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -3270,7 +3469,7 @@
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -3281,7 +3480,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>69.2%</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3492,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>5h 45m</t>
+          <t>5h 7m</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3504,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>1d 11h 36m</t>
+          <t>1d 8h 24m</t>
         </is>
       </c>
     </row>
@@ -3364,10 +3563,10 @@
         </is>
       </c>
       <c r="B11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
@@ -3559,19 +3758,19 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
@@ -3582,210 +3781,166 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>No Internet Connection</t>
+          <t>IPTV Related Issues</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>NETTV-Blank TV Display</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
           <t>Wi-Fi Range</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="D25" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>100.0%</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>Detailed Solved / Handled Tickets List</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Ticket Number</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Account Name</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D28" s="4" t="inlineStr">
         <is>
           <t>Sub Category</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>Resolution Type</t>
         </is>
       </c>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Employee Remark / Solution Note</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Action / Transfer Remark</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="I28" s="4" t="inlineStr">
         <is>
           <t>Assigned Date</t>
         </is>
       </c>
-      <c r="J27" s="4" t="inlineStr">
+      <c r="J28" s="4" t="inlineStr">
         <is>
           <t>Created Date</t>
         </is>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K28" s="4" t="inlineStr">
         <is>
           <t>Last Modified Date</t>
         </is>
       </c>
-      <c r="L27" s="4" t="inlineStr">
+      <c r="L28" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Assigned)</t>
         </is>
       </c>
-      <c r="M27" s="4" t="inlineStr">
+      <c r="M28" s="4" t="inlineStr">
         <is>
           <t>Resolution Time (From Created)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>TKT1376513</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>PRAMOD YADAV</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Hardware Damage / Malfunction</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Remote damage Issue</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="F28" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>23 Oct 2026 10:02:39 AM</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t>24 Oct 2026 11:18:54 AM</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>TKT1376631</t>
+          <t>TKT1376513</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Nirajan Raut</t>
+          <t>PRAMOD YADAV</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>General / Other Issues</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>IPTV Remote damage Issue</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -3805,22 +3960,22 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>Case : IPTV remote  has been updated by Chandramani Tharu</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 12:21:09 PM</t>
+          <t>23 Oct 2026 10:02:39 AM</t>
         </is>
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:57:25 AM</t>
+          <t>24 Oct 2026 11:18:54 AM</t>
         </is>
       </c>
       <c r="L29" s="5" t="inlineStr">
@@ -3830,19 +3985,19 @@
       </c>
       <c r="M29" s="5" t="inlineStr">
         <is>
-          <t>23h 36m</t>
+          <t>1d 1h 16m</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>TKT1376706</t>
+          <t>TKT1376631</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Ashok tamang</t>
+          <t>Nirajan Raut</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3872,22 +4027,22 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
+          <t>Case : Router Upgrade wifi 6  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>23 Oct 2026 02:17:45 PM</t>
+          <t>23 Oct 2026 12:21:09 PM</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:36:01 PM</t>
+          <t>24 Oct 2026 11:57:25 AM</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
@@ -3897,39 +4052,39 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>22h 18m</t>
+          <t>23h 36m</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>TKT1376730</t>
+          <t>TKT1376706</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>Binir Kayastha Shrestha</t>
+          <t>Ashok tamang</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Hardware Damage / Malfunction</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Router Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
@@ -3939,44 +4094,44 @@
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
+          <t>Case : Wifi - 6 Router Instal  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 03:14:20 PM</t>
+          <t>24 Oct 2026 12:36:01 PM</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 03:09:37 PM</t>
+          <t>23 Oct 2026 02:17:45 PM</t>
         </is>
       </c>
       <c r="K31" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 12:44:37 PM</t>
+          <t>24 Oct 2026 12:36:01 PM</t>
         </is>
       </c>
       <c r="L31" s="5" t="inlineStr">
         <is>
-          <t>21h 30m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M31" s="5" t="inlineStr">
         <is>
-          <t>21h 35m</t>
+          <t>22h 18m</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TKT1373677</t>
+          <t>TKT1376730</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Nisha Shrestha</t>
+          <t>Binir Kayastha Shrestha</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -3986,17 +4141,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Router Adaptor damage Issue</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Closed</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Completed (Completed)</t>
+          <t>Completed (Closed)</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -4006,64 +4161,64 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
+          <t>Case : no light blinking  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 01:22:54 PM</t>
+          <t>23 Oct 2026 03:14:20 PM</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>17 Oct 2026 02:25:13 PM</t>
+          <t>23 Oct 2026 03:09:37 PM</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 01:22:54 PM</t>
+          <t>24 Oct 2026 12:44:37 PM</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>0m</t>
+          <t>21h 30m</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>6d 22h 57m</t>
+          <t>21h 35m</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>TKT1376810</t>
+          <t>TKT1373677</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>Sonim Manandhar</t>
+          <t>Nisha Shrestha</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Wi-Fi Range</t>
+          <t>Hardware Damage / Malfunction</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Low Wi-Fi Range on both band</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Completed</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Completed (Closed)</t>
+          <t>Completed (Completed)</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
@@ -4073,54 +4228,54 @@
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
+          <t>Case : IPTV not working   has been updated by Rajesh Maharjan</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 05:36:42 PM</t>
+          <t>24 Oct 2026 01:22:54 PM</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>23 Oct 2026 05:29:23 PM</t>
+          <t>17 Oct 2026 02:25:13 PM</t>
         </is>
       </c>
       <c r="K33" s="5" t="inlineStr">
         <is>
-          <t>24 Oct 2026 01:34:40 PM</t>
+          <t>24 Oct 2026 01:22:54 PM</t>
         </is>
       </c>
       <c r="L33" s="5" t="inlineStr">
         <is>
-          <t>19h 57m</t>
+          <t>0m</t>
         </is>
       </c>
       <c r="M33" s="5" t="inlineStr">
         <is>
-          <t>20h 5m</t>
+          <t>6d 22h 57m</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TKT1377162</t>
+          <t>TKT1376810</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Jyoti Sharma</t>
+          <t>Sonim Manandhar</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>IPTV Related Issues</t>
+          <t>Wi-Fi Range</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>NETTV-Blank TV Display</t>
+          <t>Low Wi-Fi Range on both band</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -4140,32 +4295,32 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+          <t>Case : wifi  range   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:47:54 AM</t>
+          <t>23 Oct 2026 05:36:42 PM</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 11:34:32 AM</t>
+          <t>23 Oct 2026 05:29:23 PM</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>24 Oct 2026 02:06:12 PM</t>
+          <t>24 Oct 2026 01:34:40 PM</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>2h 18m</t>
+          <t>19h 57m</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>2h 31m</t>
+          <t>20h 5m</t>
         </is>
       </c>
     </row>
@@ -4233,6 +4388,140 @@
       <c r="M35" s="5" t="inlineStr">
         <is>
           <t>2h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1377162</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Jyoti Sharma</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Blank TV Display</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:47:54 AM</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 11:34:32 AM</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 02:06:12 PM</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>2h 18m</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>2h 31m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TKT1377051</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Chandra Bahadur shrestha</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:31:45 PM</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 09:47:23 AM</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>24 Oct 2026 04:31:45 PM</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>6h 44m</t>
         </is>
       </c>
     </row>

--- a/audit_report_ALL_TEAM_24_Oct_2026.xlsx
+++ b/audit_report_ALL_TEAM_24_Oct_2026.xlsx
@@ -529,7 +529,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="40" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3275,10 +3275,8 @@
           <t>Chandra Bahadur shrestha</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9841598179</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9841598179</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3368,10 +3366,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
@@ -3382,7 +3378,7 @@
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
@@ -3431,7 +3427,7 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="27" customWidth="1" min="9" max="9"/>
     <col width="27" customWidth="1" min="10" max="10"/>
@@ -4491,7 +4487,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
